--- a/reports/denim_size_report.xlsx
+++ b/reports/denim_size_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,20 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>LINK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>GENDER</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>LINK</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>Extracted Size Chart</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
+        <is>
+          <t>Reference Size Chart</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Final Size Chart Verdict</t>
         </is>
@@ -451,58 +456,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40AC805340</t>
+          <t>CKS26MMKT0086</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Polo</t>
+          <t>POLO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/40616258</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/32008231</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>MEN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Correct</t>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40BC236002</t>
+          <t>4RB862G410</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Polo</t>
+          <t>T-SHIRT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/35918718</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/33194405</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S-40, M-42, L-44, XL-46, XXL-48</t>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>XS-40, S-42, M-44, L-46, XL-48, XXL-50</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
@@ -511,30 +530,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40BC236111</t>
+          <t>4RB862G001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Polo</t>
+          <t>T-SHIRT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/35918788</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/37938959</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S-40, M-42, L-44, XL-46, XXL-48</t>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
@@ -543,30 +567,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>40BM105001</t>
+          <t>40HM228002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shirt</t>
+          <t>T-SHIRT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/36765149</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/32106413</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M-38, S-40, L-42, XL-44, XXL-46</t>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
@@ -575,30 +604,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>40BM105230</t>
+          <t>CKS26MMKT0061</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shirt</t>
+          <t>T-SHIRT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/40171523</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/32106414</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S-40, M-38, L-42, XL-44, XXL-46</t>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>XS-40, S-42, M-44, L-46, XL-48, XXL-50</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
@@ -607,30 +641,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40BM108110</t>
+          <t>4LF208G251</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shirt</t>
+          <t>POLO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/39248325</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/35190805</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>XS-36, S-37, M-38, L-40, XL-42, XXL-44</t>
+          <t>S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
@@ -639,30 +678,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40BM127062</t>
+          <t>CKS26MMKT0063</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shirt</t>
+          <t>T-SHIRT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/40171502</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/36228999</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>XS-35, S-37, M-38, L-40, XL-42, XXL-44</t>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
@@ -671,62 +715,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40BM127280</t>
+          <t>CKS26MMKT0056</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shirt</t>
+          <t>POLO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/40171499</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/36229000</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>XS-35, S-37, M-38, L-40, XL-42, XXL-44</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Incorrect</t>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40BM333001</t>
+          <t>40HM281075</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sweater</t>
+          <t>POLO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/38551479</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/34741710</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>XS-37, S-38, M-40, L-42, XL-44</t>
+          <t>S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>
@@ -735,62 +785,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40BM343001</t>
+          <t>CKS26MMKT0064</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sweater</t>
+          <t>POLO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/40171532</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/36654183</t>
+          <t>MEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S-38, M-40, L-42, XL-44, XXL-46</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Incorrect</t>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>40BM343811</t>
+          <t>47E819G001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sweater</t>
+          <t>T-SHIRT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/38776877</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/36078101</t>
+          <t>WOMEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S-38, M-40, L-42, XL-44</t>
+          <t>XS-32, S-34, M-36, L-38, XL-40</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
+        <is>
+          <t>XXS-30, XS-32, S-34, M-36, L-38, XL-40, XXL-42</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -799,30 +855,175 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>40BM347001</t>
+          <t>4RD255G603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sweater</t>
+          <t>POLO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mens Apparel</t>
+          <t>https://www.myntra.com/38776827</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.myntra.com/36078103</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>S-38, M-40, L-42, XL-44, XXL-46</t>
-        </is>
-      </c>
+          <t>MEN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4RD255G251</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>POLO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.myntra.com/38776770</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MEN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4LF250G001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>POLO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.myntra.com/39107532</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MEN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4RD255G650</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>POLO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.myntra.com/38776831</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MEN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>XS-35, S-37, M-38, L-40, XL-42, XXL-48</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Incorrect</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4LB145G110</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SHIRT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.myntra.com/35950255</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MEN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>XS-35, S-37, M-38, L-40, XL-42, XXL-48</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Incorrect</t>
         </is>

--- a/reports/denim_size_report.xlsx
+++ b/reports/denim_size_report.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+          <t>XS-40, S-42, M-44, L-46, XL-48, XXL-50</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -661,17 +661,13 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S-40, M-42, L-44, XL-46, XXL-48</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
-        </is>
-      </c>
+          <t>OUT OF STOCK</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Incorrect</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -703,7 +699,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+          <t>XS-40, S-42, M-44, L-46, XL-48, XXL-50</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -735,13 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -805,13 +805,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ERROR</t>
+          <t>Incorrect</t>
         </is>
       </c>
     </row>
@@ -873,15 +877,15 @@
           <t>MEN</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OUT OF STOCK</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Correct</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -906,15 +910,15 @@
           <t>MEN</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OUT OF STOCK</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Correct</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -941,17 +945,13 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>XS-36, S-38, M-40, L-42, XL-44, XXL-46</t>
-        </is>
-      </c>
+          <t>OUT OF STOCK</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Incorrect</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>XS-35, S-37, M-38, L-40, XL-42, XXL-48</t>
+          <t>XS-38, S-40, M-42, L-44, XL-46, XXL-48</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
